--- a/2026/SAEN PEÑA/Febrero/SAENZ_EXPENSAS-Febrero.xlsx
+++ b/2026/SAEN PEÑA/Febrero/SAENZ_EXPENSAS-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SAEN PEÑA\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\SAEN PEÑA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B943834-E04F-44D7-A0DA-6B8601658A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB20A85-843E-4D0C-ADB3-21C94C55D5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,20 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$35</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -262,7 +275,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,13 +383,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1066,7 +1072,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1273,7 +1279,6 @@
     <xf numFmtId="168" fontId="14" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="14" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="10" fillId="6" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="6" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1342,12 +1347,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1712,22 +1715,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" customWidth="1"/>
+    <col min="5" max="5" width="58.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1735,27 +1738,27 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1767,7 +1770,7 @@
       </c>
       <c r="F7" s="98"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1775,43 +1778,43 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="101" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="97"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="129" t="s">
+      <c r="E11" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="129"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" s="128"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="99"/>
       <c r="B12" s="99"/>
-      <c r="C12" s="122"/>
+      <c r="C12" s="105"/>
       <c r="D12" s="5"/>
       <c r="E12" s="48" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="121">
-        <v>1616917.9192361401</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1714239.3492361403</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="97" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="149">
+      <c r="C13" s="105">
         <v>37185.11</v>
       </c>
       <c r="D13" s="36"/>
@@ -1820,17 +1823,17 @@
       </c>
       <c r="F13" s="50">
         <f>'prorrateo '!F11</f>
-        <v>344271.84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>408115.52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="99" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="149">
+      <c r="C14" s="105">
         <v>43790.22</v>
       </c>
       <c r="D14" s="5"/>
@@ -1842,7 +1845,7 @@
         <v>-251729.53</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="97" t="s">
         <v>21</v>
       </c>
@@ -1856,12 +1859,12 @@
       <c r="E15" s="49"/>
       <c r="F15" s="50"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="99" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="97"/>
-      <c r="C16" s="150">
+      <c r="C16" s="71">
         <v>10568</v>
       </c>
       <c r="D16" s="5"/>
@@ -1871,10 +1874,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="102"/>
       <c r="B17" s="103"/>
-      <c r="C17" s="126">
+      <c r="C17" s="125">
         <f>SUM(C12:C16)</f>
         <v>126543.33</v>
       </c>
@@ -1883,20 +1886,20 @@
       </c>
       <c r="F17" s="118">
         <f>SUM(F12:F15)</f>
-        <v>1709460.2292361401</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1870625.3392361405</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="101" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="97"/>
-      <c r="C18" s="127"/>
+      <c r="C18" s="126"/>
       <c r="D18" s="5"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="97" t="s">
         <v>42</v>
       </c>
@@ -1911,7 +1914,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="97" t="s">
         <v>68</v>
       </c>
@@ -1923,45 +1926,42 @@
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="97" t="s">
         <v>67</v>
       </c>
       <c r="B21" s="104"/>
-      <c r="C21" s="105">
-        <f>400000-246950.4</f>
-        <v>153049.60000000001</v>
-      </c>
+      <c r="C21" s="105"/>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="102"/>
       <c r="B22" s="103"/>
       <c r="C22" s="119">
         <f>SUM(C18:C21)</f>
-        <v>278235.8</v>
+        <v>125186.2</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="47"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="40" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="41"/>
       <c r="C23" s="120">
         <f>+C22+C17</f>
-        <v>404779.13</v>
+        <v>251729.53</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="60" t="s">
         <v>27</v>
       </c>
@@ -1970,18 +1970,18 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="37"/>
       <c r="B26" s="28"/>
       <c r="C26" s="46"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="44"/>
       <c r="B27" s="43"/>
       <c r="C27" s="45">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="52"/>
       <c r="B28" s="53"/>
       <c r="C28" s="45">
@@ -1997,19 +1997,19 @@
       </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="69"/>
       <c r="B29" s="70"/>
       <c r="C29" s="72"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="69"/>
       <c r="B30" s="76"/>
       <c r="C30" s="77"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="69"/>
       <c r="B31" s="75"/>
       <c r="C31" s="72">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="54" t="s">
         <v>25</v>
       </c>
@@ -2027,91 +2027,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="122">
         <f>C23-C21</f>
         <v>251729.53</v>
       </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="124">
+      <c r="C34" s="123">
         <f>+C23</f>
-        <v>404779.13</v>
+        <v>251729.53</v>
       </c>
       <c r="E34" s="100"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B35" s="55"/>
-      <c r="C35" s="125">
+      <c r="C35" s="124">
         <f>C33</f>
         <v>251729.53</v>
       </c>
       <c r="E35" s="16"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D43" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D44" s="16"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="19"/>
       <c r="B56" s="18"/>
       <c r="C56" s="20"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="18"/>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="18"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
@@ -2136,24 +2136,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" customWidth="1"/>
+    <col min="11" max="11" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
@@ -2171,11 +2171,11 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="62">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="63" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de FEBRERO</v>
@@ -2194,7 +2194,7 @@
       <c r="K2" s="67"/>
       <c r="L2" s="68"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2262,7 +2262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2276,23 +2276,23 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>465043.63838215801</v>
+        <v>564587.30400625931</v>
       </c>
       <c r="F5" s="71"/>
       <c r="G5" s="58">
         <f>E5-F5</f>
-        <v>465043.63838215801</v>
+        <v>564587.30400625931</v>
       </c>
       <c r="H5" s="61">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>39063.665624101275</v>
+        <v>47425.333536525788</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="31">
         <f>K1*D5</f>
-        <v>60480</v>
+        <v>37800</v>
       </c>
       <c r="K5" s="15">
         <f>K2*D5</f>
@@ -2300,10 +2300,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>564587.30400625931</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>649812.63754278515</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2317,11 +2317,11 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>130791.84000000003</v>
-      </c>
-      <c r="F6" s="128">
+        <v>62760.000000000007</v>
+      </c>
+      <c r="F6" s="127">
         <f>E6</f>
-        <v>130791.84000000003</v>
+        <v>62760.000000000007</v>
       </c>
       <c r="G6" s="58">
         <f t="shared" ref="G6:G8" si="0">E6-F6</f>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="J6" s="31">
         <f>K1*D6</f>
-        <v>62760.000000000007</v>
+        <v>39225</v>
       </c>
       <c r="K6" s="15">
         <f>K2*D6</f>
@@ -2344,10 +2344,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>62760.000000000007</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>39225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2361,23 +2361,26 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>63280</v>
-      </c>
-      <c r="F7" s="128"/>
+        <v>131875.52000000002</v>
+      </c>
+      <c r="F7" s="127">
+        <f>E7</f>
+        <v>131875.52000000002</v>
+      </c>
       <c r="G7" s="58">
         <f t="shared" si="0"/>
-        <v>63280</v>
+        <v>0</v>
       </c>
       <c r="H7" s="61">
         <f t="shared" si="1"/>
-        <v>5315.52</v>
+        <v>0</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="31">
         <f>K1*D7</f>
-        <v>63280</v>
+        <v>39550</v>
       </c>
       <c r="K7" s="15">
         <f>K2*D7</f>
@@ -2385,10 +2388,10 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="2">J7+K7+H7+G7</f>
-        <v>131875.52000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>39550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2404,7 +2407,7 @@
       <c r="E8" s="34">
         <v>79200</v>
       </c>
-      <c r="F8" s="128">
+      <c r="F8" s="127">
         <f>E8</f>
         <v>79200</v>
       </c>
@@ -2421,7 +2424,7 @@
       </c>
       <c r="J8" s="31">
         <f>K1*D8</f>
-        <v>79200</v>
+        <v>49500</v>
       </c>
       <c r="K8" s="15">
         <f>K2*D8</f>
@@ -2429,10 +2432,10 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="2"/>
-        <v>79200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2448,7 +2451,7 @@
       <c r="E9" s="34">
         <v>63680</v>
       </c>
-      <c r="F9" s="128">
+      <c r="F9" s="127">
         <f>E9</f>
         <v>63680</v>
       </c>
@@ -2465,7 +2468,7 @@
       </c>
       <c r="J9" s="31">
         <f>K1*D9</f>
-        <v>63680</v>
+        <v>39800</v>
       </c>
       <c r="K9" s="15">
         <f>K2*D9</f>
@@ -2473,10 +2476,10 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="2"/>
-        <v>63680</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>39800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2492,7 +2495,7 @@
       <c r="E10" s="34">
         <v>70600</v>
       </c>
-      <c r="F10" s="128">
+      <c r="F10" s="127">
         <f>E10</f>
         <v>70600</v>
       </c>
@@ -2509,7 +2512,7 @@
       </c>
       <c r="J10" s="31">
         <f>K1*D10</f>
-        <v>70600</v>
+        <v>44125</v>
       </c>
       <c r="K10" s="15">
         <f>K2*D10</f>
@@ -2517,10 +2520,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>70600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>44125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2532,19 +2535,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="3">SUM(E5:E10)</f>
-        <v>872595.47838215809</v>
+        <v>972702.82400625932</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>344271.84</v>
+        <v>408115.52</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>528323.63838215801</v>
+        <v>564587.30400625931</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="4">SUM(H5:H10)</f>
-        <v>44379.185624101272</v>
+        <v>47425.333536525788</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="4"/>
@@ -2552,7 +2555,7 @@
       </c>
       <c r="J11" s="39">
         <f t="shared" si="4"/>
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="4"/>
@@ -2560,27 +2563,27 @@
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>972702.82400625932</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="130"/>
-      <c r="B12" s="130"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>862012.63754278515</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="129"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2600,21 +2603,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.6328125" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="106" t="s">
         <v>69</v>
       </c>
@@ -2623,13 +2626,13 @@
       <c r="D1" s="108"/>
       <c r="E1" s="109"/>
       <c r="F1" s="108"/>
-      <c r="G1" s="131">
+      <c r="G1" s="130">
         <v>4500000</v>
       </c>
-      <c r="H1" s="131"/>
+      <c r="H1" s="130"/>
       <c r="I1" s="110"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2658,7 +2661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2679,7 +2682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2711,7 +2714,7 @@
         <v>680400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2743,7 +2746,7 @@
         <v>706050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -2775,7 +2778,7 @@
         <v>711900</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -2807,7 +2810,7 @@
         <v>891000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -2839,7 +2842,7 @@
         <v>716400</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -2871,7 +2874,7 @@
         <v>794250</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="113" t="s">
         <v>10</v>
       </c>
@@ -2902,21 +2905,21 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="130"/>
-      <c r="B11" s="130"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="129"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
@@ -2934,68 +2937,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="137" t="s">
+    <row r="1" spans="1:7" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="136" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="139"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="138"/>
       <c r="F1" s="78"/>
       <c r="G1" s="78"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="140" t="s">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="143">
+      <c r="B2" s="140"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142">
         <v>565</v>
       </c>
-      <c r="E2" s="144"/>
+      <c r="E2" s="143"/>
       <c r="F2" s="79"/>
       <c r="G2" s="79"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="145" t="s">
+    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="145" t="s">
+      <c r="C3" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="147" t="s">
+      <c r="D3" s="146" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="132" t="s">
+      <c r="E3" s="131" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="132" t="s">
+      <c r="F3" s="131" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="132" t="s">
+      <c r="G3" s="131" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="146"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="148"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="145"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="80">
         <v>1</v>
       </c>
@@ -3018,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="80">
         <v>2</v>
       </c>
@@ -3041,7 +3044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="80">
         <v>3</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="80">
         <v>4</v>
       </c>
@@ -3087,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="80">
         <v>5</v>
       </c>
@@ -3110,7 +3113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="85">
         <v>6</v>
       </c>
@@ -3133,7 +3136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="90" t="s">
         <v>10</v>
       </c>
@@ -3152,12 +3155,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="134"/>
-      <c r="B12" s="135"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="136"/>
+    <row r="12" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="133"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="135"/>
       <c r="F12" s="78"/>
       <c r="G12" s="78"/>
     </row>
